--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000752</v>
+        <v>118000727</v>
       </c>
       <c r="B11" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,47 +1801,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698154</v>
+        <v>698075</v>
       </c>
       <c r="R11" t="n">
-        <v>6360659</v>
+        <v>6360628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,11 +1865,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000727</v>
+        <v>118000752</v>
       </c>
       <c r="B12" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,38 +1908,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698075</v>
+        <v>698154</v>
       </c>
       <c r="R12" t="n">
-        <v>6360628</v>
+        <v>6360659</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1986,6 +1981,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000721</v>
+        <v>118000786</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,34 +2489,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R17" t="n">
-        <v>6360663</v>
+        <v>6360654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,11 +2568,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000786</v>
+        <v>118000721</v>
       </c>
       <c r="B18" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,53 +2615,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698159</v>
+        <v>698064</v>
       </c>
       <c r="R18" t="n">
-        <v>6360654</v>
+        <v>6360663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2680,6 +2675,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118000791</v>
+        <v>118000793</v>
       </c>
       <c r="B2" t="n">
         <v>42953</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698105</v>
+        <v>698144</v>
       </c>
       <c r="R2" t="n">
-        <v>6360598</v>
+        <v>6360649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,6 +770,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118000737</v>
+        <v>118000753</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +818,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698100</v>
+        <v>698154</v>
       </c>
       <c r="R3" t="n">
-        <v>6360609</v>
+        <v>6360659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118000782</v>
+        <v>118000746</v>
       </c>
       <c r="B4" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,56 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698223</v>
+        <v>698134</v>
       </c>
       <c r="R4" t="n">
-        <v>6360767</v>
+        <v>6360639</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118000781</v>
+        <v>118000749</v>
       </c>
       <c r="B5" t="n">
-        <v>42953</v>
+        <v>97754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,17 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698223</v>
+        <v>698144</v>
       </c>
       <c r="R5" t="n">
-        <v>6360777</v>
+        <v>6360649</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118000783</v>
+        <v>118000721</v>
       </c>
       <c r="B6" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,56 +1152,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698216</v>
+        <v>698064</v>
       </c>
       <c r="R6" t="n">
-        <v>6360742</v>
+        <v>6360663</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,6 +1212,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118000795</v>
+        <v>118000752</v>
       </c>
       <c r="B7" t="n">
-        <v>42953</v>
+        <v>102044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,45 +1260,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698185</v>
+        <v>698154</v>
       </c>
       <c r="R7" t="n">
-        <v>6360629</v>
+        <v>6360659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,6 +1335,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1403,7 +1351,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Glänta i kalkbarrskog.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1421,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118000831</v>
+        <v>118000790</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>42953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,35 +1381,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1470,13 +1428,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698109</v>
+        <v>698064</v>
       </c>
       <c r="R8" t="n">
-        <v>6360613</v>
+        <v>6360688</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118000794</v>
+        <v>118000780</v>
       </c>
       <c r="B9" t="n">
         <v>42953</v>
@@ -1596,13 +1554,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698154</v>
+        <v>698230</v>
       </c>
       <c r="R9" t="n">
-        <v>6360659</v>
+        <v>6360781</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1663,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118000792</v>
+        <v>118000783</v>
       </c>
       <c r="B10" t="n">
         <v>42953</v>
@@ -1722,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698134</v>
+        <v>698216</v>
       </c>
       <c r="R10" t="n">
-        <v>6360639</v>
+        <v>6360742</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000727</v>
+        <v>118000791</v>
       </c>
       <c r="B11" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,34 +1763,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698075</v>
+        <v>698105</v>
       </c>
       <c r="R11" t="n">
-        <v>6360628</v>
+        <v>6360598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1896,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000752</v>
+        <v>118000785</v>
       </c>
       <c r="B12" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,25 +1885,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1936,7 +1913,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1945,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698154</v>
+        <v>698174</v>
       </c>
       <c r="R12" t="n">
-        <v>6360659</v>
+        <v>6360672</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,11 +1968,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118000749</v>
+        <v>118000792</v>
       </c>
       <c r="B13" t="n">
-        <v>97754</v>
+        <v>42953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,25 +2011,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2057,7 +2039,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2066,10 +2058,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698144</v>
+        <v>698134</v>
       </c>
       <c r="R13" t="n">
-        <v>6360649</v>
+        <v>6360639</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118000753</v>
+        <v>118000832</v>
       </c>
       <c r="B14" t="n">
-        <v>108703</v>
+        <v>56598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,41 +2137,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698154</v>
+        <v>698134</v>
       </c>
       <c r="R14" t="n">
-        <v>6360659</v>
+        <v>6360639</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2240,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118000780</v>
+        <v>118000831</v>
       </c>
       <c r="B15" t="n">
-        <v>42953</v>
+        <v>57656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,25 +2253,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101242</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2278,19 +2279,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2299,13 +2290,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698230</v>
+        <v>698109</v>
       </c>
       <c r="R15" t="n">
-        <v>6360781</v>
+        <v>6360613</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118000746</v>
+        <v>118000737</v>
       </c>
       <c r="B16" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,38 +2369,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698134</v>
+        <v>698100</v>
       </c>
       <c r="R16" t="n">
-        <v>6360639</v>
+        <v>6360609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000786</v>
+        <v>118000727</v>
       </c>
       <c r="B17" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,53 +2489,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698159</v>
+        <v>698075</v>
       </c>
       <c r="R17" t="n">
-        <v>6360654</v>
+        <v>6360628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2599,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000721</v>
+        <v>118000782</v>
       </c>
       <c r="B18" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,37 +2596,56 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698064</v>
+        <v>698223</v>
       </c>
       <c r="R18" t="n">
-        <v>6360663</v>
+        <v>6360767</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2675,11 +2675,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,7 +2706,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000793</v>
+        <v>118000794</v>
       </c>
       <c r="B19" t="n">
         <v>42953</v>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698144</v>
+        <v>698154</v>
       </c>
       <c r="R19" t="n">
-        <v>6360649</v>
+        <v>6360659</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2806,11 +2801,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118000832</v>
+        <v>118000795</v>
       </c>
       <c r="B20" t="n">
-        <v>56598</v>
+        <v>42953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,35 +2844,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100038</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698134</v>
+        <v>698185</v>
       </c>
       <c r="R20" t="n">
-        <v>6360639</v>
+        <v>6360629</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Glänta i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118000785</v>
+        <v>118000781</v>
       </c>
       <c r="B21" t="n">
         <v>42953</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698174</v>
+        <v>698223</v>
       </c>
       <c r="R21" t="n">
-        <v>6360672</v>
+        <v>6360777</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118000790</v>
+        <v>118000786</v>
       </c>
       <c r="B22" t="n">
         <v>42953</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R22" t="n">
-        <v>6360688</v>
+        <v>6360654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118000793</v>
+        <v>118000794</v>
       </c>
       <c r="B2" t="n">
         <v>42953</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698144</v>
+        <v>698154</v>
       </c>
       <c r="R2" t="n">
-        <v>6360649</v>
+        <v>6360659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118000753</v>
+        <v>118000749</v>
       </c>
       <c r="B3" t="n">
-        <v>108703</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698154</v>
+        <v>698144</v>
       </c>
       <c r="R3" t="n">
-        <v>6360659</v>
+        <v>6360649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118000746</v>
+        <v>118000727</v>
       </c>
       <c r="B4" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698134</v>
+        <v>698075</v>
       </c>
       <c r="R4" t="n">
-        <v>6360639</v>
+        <v>6360628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118000749</v>
+        <v>118000831</v>
       </c>
       <c r="B5" t="n">
-        <v>97754</v>
+        <v>57657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,9 +1062,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698144</v>
+        <v>698109</v>
       </c>
       <c r="R5" t="n">
-        <v>6360649</v>
+        <v>6360613</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118000721</v>
+        <v>118000786</v>
       </c>
       <c r="B6" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1156,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R6" t="n">
-        <v>6360663</v>
+        <v>6360654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,11 +1235,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118000752</v>
+        <v>118000792</v>
       </c>
       <c r="B7" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,7 +1306,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698154</v>
+        <v>698134</v>
       </c>
       <c r="R7" t="n">
-        <v>6360659</v>
+        <v>6360639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,11 +1361,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118000790</v>
+        <v>118000793</v>
       </c>
       <c r="B8" t="n">
         <v>42953</v>
@@ -1404,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1428,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698064</v>
+        <v>698144</v>
       </c>
       <c r="R8" t="n">
-        <v>6360688</v>
+        <v>6360649</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,6 +1487,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118000780</v>
+        <v>118000746</v>
       </c>
       <c r="B9" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,56 +1539,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698230</v>
+        <v>698134</v>
       </c>
       <c r="R9" t="n">
-        <v>6360781</v>
+        <v>6360639</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,7 +1630,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118000783</v>
+        <v>118000785</v>
       </c>
       <c r="B10" t="n">
         <v>42953</v>
@@ -1680,13 +1689,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698216</v>
+        <v>698174</v>
       </c>
       <c r="R10" t="n">
-        <v>6360742</v>
+        <v>6360672</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1747,7 +1756,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000791</v>
+        <v>118000782</v>
       </c>
       <c r="B11" t="n">
         <v>42953</v>
@@ -1782,7 +1791,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1806,13 +1815,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698105</v>
+        <v>698223</v>
       </c>
       <c r="R11" t="n">
-        <v>6360598</v>
+        <v>6360767</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000785</v>
+        <v>118000737</v>
       </c>
       <c r="B12" t="n">
-        <v>42953</v>
+        <v>97860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,45 +1894,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101242</v>
+        <v>219862</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1932,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698174</v>
+        <v>698100</v>
       </c>
       <c r="R12" t="n">
-        <v>6360672</v>
+        <v>6360609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,10 +1998,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118000792</v>
+        <v>118000752</v>
       </c>
       <c r="B13" t="n">
-        <v>42953</v>
+        <v>102046</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,25 +2010,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2039,17 +2038,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2058,10 +2047,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698134</v>
+        <v>698154</v>
       </c>
       <c r="R13" t="n">
-        <v>6360639</v>
+        <v>6360659</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,6 +2083,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118000832</v>
+        <v>118000721</v>
       </c>
       <c r="B14" t="n">
-        <v>56598</v>
+        <v>108705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,50 +2131,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698134</v>
+        <v>698064</v>
       </c>
       <c r="R14" t="n">
-        <v>6360639</v>
+        <v>6360663</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,6 +2195,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2241,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118000831</v>
+        <v>118000832</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>56599</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,21 +2247,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2290,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698109</v>
+        <v>698134</v>
       </c>
       <c r="R15" t="n">
-        <v>6360613</v>
+        <v>6360639</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118000737</v>
+        <v>118000791</v>
       </c>
       <c r="B16" t="n">
-        <v>97858</v>
+        <v>42953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,25 +2359,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2397,7 +2387,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698100</v>
+        <v>698105</v>
       </c>
       <c r="R16" t="n">
-        <v>6360609</v>
+        <v>6360598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000727</v>
+        <v>118000780</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,37 +2489,56 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698075</v>
+        <v>698230</v>
       </c>
       <c r="R17" t="n">
-        <v>6360628</v>
+        <v>6360781</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2580,7 +2599,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000782</v>
+        <v>118000783</v>
       </c>
       <c r="B18" t="n">
         <v>42953</v>
@@ -2639,10 +2658,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698223</v>
+        <v>698216</v>
       </c>
       <c r="R18" t="n">
-        <v>6360767</v>
+        <v>6360742</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2706,7 +2725,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000794</v>
+        <v>118000790</v>
       </c>
       <c r="B19" t="n">
         <v>42953</v>
@@ -2741,7 +2760,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2765,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698154</v>
+        <v>698064</v>
       </c>
       <c r="R19" t="n">
-        <v>6360659</v>
+        <v>6360688</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2832,7 +2851,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118000795</v>
+        <v>118000781</v>
       </c>
       <c r="B20" t="n">
         <v>42953</v>
@@ -2867,7 +2886,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2891,13 +2910,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698185</v>
+        <v>698223</v>
       </c>
       <c r="R20" t="n">
-        <v>6360629</v>
+        <v>6360777</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2940,7 +2959,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Glänta i kalkbarrskog.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2958,7 +2977,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118000781</v>
+        <v>118000795</v>
       </c>
       <c r="B21" t="n">
         <v>42953</v>
@@ -2993,7 +3012,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3017,13 +3036,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698223</v>
+        <v>698185</v>
       </c>
       <c r="R21" t="n">
-        <v>6360777</v>
+        <v>6360629</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3066,7 +3085,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Glänta i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3103,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118000786</v>
+        <v>118000753</v>
       </c>
       <c r="B22" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,53 +3119,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698159</v>
+        <v>698154</v>
       </c>
       <c r="R22" t="n">
-        <v>6360654</v>
+        <v>6360659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000752</v>
+        <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102054</v>
+        <v>102286</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>6360659</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2783,6 +2783,11 @@
           <t>Fröjel</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>I-Got-1588</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>2024-06-24</t>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
+          <t>1 träd (2 m), men nedliggande överkörd!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,16 +2811,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrskog med lundstarr.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bengt Carlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2823,7 +2823,11 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,11 +2709,11 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 34600-2019 artfynd.xlsx
+++ b/artfynd/A 34600-2019 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
